--- a/apps/snapshot/ship_cost.xlsx
+++ b/apps/snapshot/ship_cost.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\apps\snapshot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B4082AC-F612-4AF9-A5FF-FA9D9576F345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8774CC-461B-4E74-B73F-4D0F4E80919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="重量" sheetId="1" r:id="rId1"/>
+    <sheet name="サイズ" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>g</t>
     <phoneticPr fontId="1"/>
@@ -51,6 +52,10 @@
   </si>
   <si>
     <t>jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cm</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -462,6 +467,9 @@
       <c r="C2">
         <v>3458</v>
       </c>
+      <c r="D2">
+        <v>1010</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
@@ -473,6 +481,9 @@
       <c r="C3">
         <v>2979</v>
       </c>
+      <c r="D3">
+        <v>1010</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
@@ -484,6 +495,9 @@
       <c r="C4">
         <v>3458</v>
       </c>
+      <c r="D4">
+        <v>1010</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
@@ -495,6 +509,9 @@
       <c r="C5">
         <v>3935</v>
       </c>
+      <c r="D5">
+        <v>1010</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
@@ -506,6 +523,9 @@
       <c r="C6">
         <v>4383</v>
       </c>
+      <c r="D6">
+        <v>1010</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
@@ -517,6 +537,9 @@
       <c r="C7">
         <v>5317</v>
       </c>
+      <c r="D7">
+        <v>1250</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
@@ -528,6 +551,9 @@
       <c r="C8">
         <v>6476</v>
       </c>
+      <c r="D8">
+        <v>1250</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
@@ -539,6 +565,9 @@
       <c r="C9">
         <v>7891</v>
       </c>
+      <c r="D9">
+        <v>1250</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
@@ -550,6 +579,9 @@
       <c r="C10">
         <v>8733</v>
       </c>
+      <c r="D10">
+        <v>1540</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
@@ -561,6 +593,9 @@
       <c r="C11">
         <v>9407</v>
       </c>
+      <c r="D11">
+        <v>1540</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
@@ -572,6 +607,9 @@
       <c r="C12">
         <v>10080</v>
       </c>
+      <c r="D12">
+        <v>1540</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
@@ -583,6 +621,9 @@
       <c r="C13">
         <v>10752</v>
       </c>
+      <c r="D13">
+        <v>1540</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
@@ -594,6 +635,9 @@
       <c r="C14">
         <v>13054</v>
       </c>
+      <c r="D14">
+        <v>1540</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
@@ -605,6 +649,9 @@
       <c r="C15">
         <v>13883</v>
       </c>
+      <c r="D15">
+        <v>1870</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
@@ -616,8 +663,11 @@
       <c r="C16">
         <v>14714</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D16">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>13000</v>
       </c>
@@ -627,8 +677,11 @@
       <c r="C17">
         <v>16263</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D17">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>14000</v>
       </c>
@@ -638,8 +691,11 @@
       <c r="C18">
         <v>17128</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D18">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>15000</v>
       </c>
@@ -649,8 +705,11 @@
       <c r="C19">
         <v>17993</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D19">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>16000</v>
       </c>
@@ -660,8 +719,11 @@
       <c r="C20">
         <v>19493</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D20">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>17000</v>
       </c>
@@ -671,8 +733,11 @@
       <c r="C21">
         <v>20385</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D21">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>18000</v>
       </c>
@@ -682,8 +747,11 @@
       <c r="C22">
         <v>21278</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D22">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>19000</v>
       </c>
@@ -693,8 +761,11 @@
       <c r="C23">
         <v>22170</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D23">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>20000</v>
       </c>
@@ -703,6 +774,84 @@
       </c>
       <c r="C24">
         <v>23061</v>
+      </c>
+      <c r="D24">
+        <v>2110</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D662A61-3EB6-40C3-B3B1-F9749BFA90A5}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>-1</v>
+      </c>
+      <c r="B2">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>60</v>
+      </c>
+      <c r="B3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>120</v>
+      </c>
+      <c r="B6">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>140</v>
+      </c>
+      <c r="B7">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>160</v>
+      </c>
+      <c r="B8">
+        <v>2360</v>
       </c>
     </row>
   </sheetData>
